--- a/src/ii_skills/shared/excel_templates/12_portfolio_valuations.xlsx
+++ b/src/ii_skills/shared/excel_templates/12_portfolio_valuations.xlsx
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="$#,##0.0&quot;M&quot;"/>
-    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.0"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -31,13 +29,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -46,18 +46,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-        <bgColor rgb="00F0F0F0"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -65,30 +59,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -455,272 +435,203 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio Company Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Logo_Path</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Invested_M</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Current_MOIC</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Current_IRR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Exit_Date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Exit_MOIC_Low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Exit_MOIC_High</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Exit_IRR_Low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Exit_IRR_High</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Company A</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>logos/a.png</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0.397</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>H1'27</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>Company B</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>logos/b.png</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Company C</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>logos/c.png</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.253</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Invested ($M)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Current MOIC</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Current IRR</t>
+        </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>H2'26</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0.28</v>
+          <t>Exit Date</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Exit MOIC Range</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Exit IRR Range</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Company D</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>logos/d.png</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.25</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Company A</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>39.7%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>H1'27</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2.5-3.0x</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>28-34%</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Company E</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>logos/e.png</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Company B</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>H1'26</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0.38</v>
+        <v>27.2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.6x</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2.5-3.0x</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>26-32%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Company C</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.85x</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>H2'26</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.2-2.8x</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>22-28%</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>PORTFOLIO TOTAL</t>
-        </is>
-      </c>
-      <c r="C8" s="11">
-        <f>SUM(C2:C6)</f>
-        <v/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Company D</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.45x</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2.0-2.5x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20-25%</t>
+        </is>
       </c>
     </row>
   </sheetData>
